--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,8 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -537,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7189</v>
+        <v>11413</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9039</v>
+        <v>16464</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1850</v>
+        <v>-5051</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -556,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -568,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6003</v>
+        <v>11413</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6651</v>
+        <v>13570</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-648</v>
+        <v>-2157</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -599,7 +617,7 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -613,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -627,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7189</v>
+        <v>10648</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9039</v>
+        <v>24942</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1850</v>
+        <v>-14294</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -644,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -658,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -672,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9963</v>
+        <v>10648</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11123</v>
+        <v>11072</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1160</v>
+        <v>-424</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -689,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -703,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -717,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9963</v>
+        <v>10648</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11123</v>
+        <v>16464</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1160</v>
+        <v>-5816</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -734,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -748,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -762,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10681</v>
+        <v>12560</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11123</v>
+        <v>13570</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-442</v>
+        <v>-1010</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -779,237 +797,12 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>10681</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>12323</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-1642</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22-AUG-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>11454</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>12323</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-869</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>01-SEP-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>10681</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>11123</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-442</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>05-SEP-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>10681</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>11123</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-442</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>08-SEP-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>9963</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>11123</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-1160</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014B8D50-3FB3-4B16-937E-54629D5E0C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EEA542-F71E-4CFB-835C-C2327691A03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -60,39 +60,33 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>28-JUL-26</t>
+    <t>08-AUG-26</t>
+  </si>
+  <si>
+    <t>SM-447</t>
+  </si>
+  <si>
+    <t>Nile Air NP-103</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>11-AUG-26</t>
   </si>
   <si>
     <t>SM-441</t>
   </si>
   <si>
-    <t>Nile Air NP-103</t>
+    <t>15-AUG-26</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>01-AUG-26</t>
-  </si>
-  <si>
-    <t>SM-447</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>08-AUG-26</t>
-  </si>
-  <si>
-    <t>11-AUG-26</t>
-  </si>
-  <si>
-    <t>15-AUG-26</t>
-  </si>
-  <si>
     <t>18-AUG-26</t>
   </si>
   <si>
@@ -103,9 +97,6 @@
   </si>
   <si>
     <t>29-AUG-26</t>
-  </si>
-  <si>
-    <t>05-SEP-26</t>
   </si>
   <si>
     <t>08-SEP-26</t>
@@ -180,14 +171,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor rgb="FFF8D7DA"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -535,7 +526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -596,13 +587,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>12560</v>
+        <v>10648</v>
       </c>
       <c r="E2" s="2">
-        <v>13570</v>
+        <v>18061</v>
       </c>
       <c r="F2" s="2">
-        <v>-1010</v>
+        <v>-7413</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -631,13 +622,13 @@
         <v>13</v>
       </c>
       <c r="D3" s="2">
-        <v>11413</v>
+        <v>10648</v>
       </c>
       <c r="E3" s="2">
-        <v>24942</v>
+        <v>16464</v>
       </c>
       <c r="F3" s="2">
-        <v>-13529</v>
+        <v>-5816</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -648,8 +639,8 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>18</v>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>15</v>
@@ -657,34 +648,34 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2">
+        <v>12559</v>
+      </c>
+      <c r="E4" s="2">
+        <v>14962</v>
+      </c>
+      <c r="F4" s="2">
+        <v>-2403</v>
+      </c>
+      <c r="G4" s="2">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2">
-        <v>10648</v>
-      </c>
-      <c r="E4" s="2">
-        <v>18061</v>
-      </c>
-      <c r="F4" s="2">
-        <v>-7413</v>
-      </c>
-      <c r="G4" s="2">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>15</v>
@@ -695,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="2">
-        <v>10648</v>
+        <v>12559</v>
       </c>
       <c r="E5" s="2">
-        <v>16464</v>
+        <v>14962</v>
       </c>
       <c r="F5" s="2">
-        <v>-5816</v>
+        <v>-2403</v>
       </c>
       <c r="G5" s="2">
         <v>30</v>
@@ -719,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -730,19 +721,19 @@
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="2">
-        <v>12560</v>
+        <v>12559</v>
       </c>
       <c r="E6" s="2">
-        <v>14962</v>
+        <v>18061</v>
       </c>
       <c r="F6" s="2">
-        <v>-2402</v>
+        <v>-5502</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -762,7 +753,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
@@ -771,13 +762,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="2">
-        <v>12560</v>
+        <v>11413</v>
       </c>
       <c r="E7" s="2">
-        <v>13570</v>
+        <v>12273</v>
       </c>
       <c r="F7" s="2">
-        <v>-1010</v>
+        <v>-860</v>
       </c>
       <c r="G7" s="2">
         <v>30</v>
@@ -788,8 +779,8 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>14</v>
+      <c r="J7" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -797,7 +788,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -806,13 +797,13 @@
         <v>13</v>
       </c>
       <c r="D8" s="2">
-        <v>12560</v>
+        <v>11413</v>
       </c>
       <c r="E8" s="2">
-        <v>14962</v>
+        <v>12273</v>
       </c>
       <c r="F8" s="2">
-        <v>-2402</v>
+        <v>-860</v>
       </c>
       <c r="G8" s="2">
         <v>30</v>
@@ -823,8 +814,8 @@
       <c r="I8" s="2">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>14</v>
+      <c r="J8" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -832,7 +823,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -841,13 +832,13 @@
         <v>13</v>
       </c>
       <c r="D9" s="2">
-        <v>12560</v>
+        <v>10648</v>
       </c>
       <c r="E9" s="2">
-        <v>18061</v>
+        <v>11071</v>
       </c>
       <c r="F9" s="2">
-        <v>-5501</v>
+        <v>-423</v>
       </c>
       <c r="G9" s="2">
         <v>30</v>
@@ -859,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -867,22 +858,22 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="2">
-        <v>11413</v>
+        <v>16259</v>
       </c>
       <c r="E10" s="2">
-        <v>12273</v>
+        <v>24942</v>
       </c>
       <c r="F10" s="2">
-        <v>-860</v>
+        <v>-8683</v>
       </c>
       <c r="G10" s="2">
         <v>30</v>
@@ -902,7 +893,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
@@ -911,13 +902,13 @@
         <v>13</v>
       </c>
       <c r="D11" s="2">
-        <v>11413</v>
+        <v>16259</v>
       </c>
       <c r="E11" s="2">
-        <v>12273</v>
+        <v>24942</v>
       </c>
       <c r="F11" s="2">
-        <v>-860</v>
+        <v>-8683</v>
       </c>
       <c r="G11" s="2">
         <v>30</v>
@@ -937,7 +928,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
@@ -946,13 +937,13 @@
         <v>13</v>
       </c>
       <c r="D12" s="2">
-        <v>10648</v>
+        <v>16259</v>
       </c>
       <c r="E12" s="2">
-        <v>11072</v>
+        <v>24942</v>
       </c>
       <c r="F12" s="2">
-        <v>-424</v>
+        <v>-8683</v>
       </c>
       <c r="G12" s="2">
         <v>30</v>
@@ -972,22 +963,22 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="2">
-        <v>9938</v>
+        <v>16259</v>
       </c>
       <c r="E13" s="2">
-        <v>11072</v>
+        <v>24942</v>
       </c>
       <c r="F13" s="2">
-        <v>-1134</v>
+        <v>-8683</v>
       </c>
       <c r="G13" s="2">
         <v>30</v>
@@ -1007,10 +998,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>13</v>
@@ -1033,8 +1024,8 @@
       <c r="I14" s="2">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>18</v>
+      <c r="J14" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1042,10 +1033,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>13</v>
@@ -1068,8 +1059,8 @@
       <c r="I15" s="2">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>18</v>
+      <c r="J15" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1077,10 +1068,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>13</v>
@@ -1103,8 +1094,8 @@
       <c r="I16" s="2">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>18</v>
+      <c r="J16" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1112,10 +1103,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>13</v>
@@ -1138,8 +1129,8 @@
       <c r="I17" s="2">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>18</v>
+      <c r="J17" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1147,10 +1138,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>13</v>
@@ -1173,8 +1164,8 @@
       <c r="I18" s="2">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>18</v>
+      <c r="J18" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1182,10 +1173,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>13</v>
@@ -1208,150 +1199,10 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>18</v>
+      <c r="J19" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2">
-        <v>16259</v>
-      </c>
-      <c r="E20" s="2">
-        <v>24942</v>
-      </c>
-      <c r="F20" s="2">
-        <v>-8683</v>
-      </c>
-      <c r="G20" s="2">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="2">
-        <v>16259</v>
-      </c>
-      <c r="E21" s="2">
-        <v>24942</v>
-      </c>
-      <c r="F21" s="2">
-        <v>-8683</v>
-      </c>
-      <c r="G21" s="2">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="2">
-        <v>16259</v>
-      </c>
-      <c r="E22" s="2">
-        <v>24942</v>
-      </c>
-      <c r="F22" s="2">
-        <v>-8683</v>
-      </c>
-      <c r="G22" s="2">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="2">
-        <v>16259</v>
-      </c>
-      <c r="E23" s="2">
-        <v>24942</v>
-      </c>
-      <c r="F23" s="2">
-        <v>-8683</v>
-      </c>
-      <c r="G23" s="2">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="2" t="s">
         <v>15</v>
       </c>
     </row>
